--- a/src/database/test/test_email_sheet.xlsx
+++ b/src/database/test/test_email_sheet.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Repositories\XpressCredentialling\src\database\test\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C918874D-1335-4A36-8598-4A50CC480522}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C993733-1B95-4370-ABC1-36DCFAFA91F9}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="9060" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
